--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -1749,7 +1749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2055,46 +2055,63 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>73</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>manastone</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>魔晶石</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🟪</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>manaSteal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>吸魔</t>
+        </is>
       </c>
       <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>54</v>
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
         <v>54</v>
@@ -2102,68 +2119,65 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F16">
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -2177,45 +2191,48 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F19">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="s">
         <v>54</v>
@@ -2223,22 +2240,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2246,22 +2263,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="s">
         <v>54</v>
@@ -2269,22 +2286,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F23">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G23" t="s">
         <v>54</v>
@@ -2292,19 +2309,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F24">
         <v>0.8</v>
@@ -2315,45 +2332,42 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2367,19 +2381,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2393,19 +2407,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2419,19 +2433,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2445,19 +2459,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E30" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2471,19 +2485,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2497,19 +2511,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E32" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2523,19 +2537,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C33" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E33" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2549,19 +2563,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -2575,19 +2589,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2601,19 +2615,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -2627,19 +2641,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -2653,19 +2667,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2679,19 +2693,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D39" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E39" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -2705,19 +2719,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C40" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D40" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -2731,22 +2745,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C41" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G41" t="s">
         <v>54</v>
@@ -2757,19 +2771,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C42" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D42" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E42" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F42">
         <v>5</v>
@@ -2783,19 +2797,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C43" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D43" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E43" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -2809,19 +2823,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E44" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F44">
         <v>5</v>
@@ -2835,19 +2849,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D45" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -2861,19 +2875,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -2887,19 +2901,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D47" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E47" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F47">
         <v>5</v>
@@ -2913,19 +2927,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C48" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E48" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F48">
         <v>5</v>
@@ -2939,27 +2953,53 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49" t="s">
+        <v>54</v>
+      </c>
+      <c r="H49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>244</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>245</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>246</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>247</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E50" t="s">
         <v>248</v>
       </c>
-      <c r="F49">
+      <c r="F50">
         <v>1</v>
       </c>
-      <c r="G49" t="s">
-        <v>54</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="G50" t="s">
+        <v>54</v>
+      </c>
+      <c r="H50" t="s">
         <v>54</v>
       </c>
     </row>
